--- a/02_HRvLR_groups/Figures/S03_Signatures/c_data/s03_signatures.xlsx
+++ b/02_HRvLR_groups/Figures/S03_Signatures/c_data/s03_signatures.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="159">
   <si>
     <t>sheet</t>
   </si>
@@ -150,19 +150,19 @@
     <t>contrasts</t>
   </si>
   <si>
-    <t>02_Proteins/02_Contrasts/c_data/02_contrasts.xlsx</t>
-  </si>
-  <si>
-    <t>6ee0f62be35c4b0f3a9281eccdf490b2</t>
+    <t>02_HRvLR_groups/02_DEP/c_data/02_contrasts.xlsx</t>
+  </si>
+  <si>
+    <t>4deff25d883e1dc54781cd410d78344b</t>
   </si>
   <si>
     <t>set_tests</t>
   </si>
   <si>
-    <t>03_Pathways/03_Contrasts/c_data/set_tests.rds</t>
-  </si>
-  <si>
-    <t>52c365ae84d1f5f25d3e280360d861dd</t>
+    <t>02_HRvLR_groups/03_Pathways/c_data/set_tests.rds</t>
+  </si>
+  <si>
+    <t>068c220be1f09313a9955fa01f855602</t>
   </si>
   <si>
     <t>package</t>
@@ -399,9 +399,6 @@
     <t>2.6.1</t>
   </si>
   <si>
-    <t>ragg</t>
-  </si>
-  <si>
     <t>RColorBrewer</t>
   </si>
   <si>
@@ -475,12 +472,6 @@
   </si>
   <si>
     <t>1.5.1</t>
-  </si>
-  <si>
-    <t>systemfonts</t>
-  </si>
-  <si>
-    <t>textshaping</t>
   </si>
   <si>
     <t>tibble</t>
@@ -1211,10 +1202,10 @@
         <v>35</v>
       </c>
       <c r="F4">
-        <v>-0.6177853391882463</v>
+        <v>-0.6143758522343953</v>
       </c>
       <c r="G4">
-        <v>0.1819452873637136</v>
+        <v>0.1780293523942687</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1234,10 +1225,10 @@
         <v>35</v>
       </c>
       <c r="F5">
-        <v>-0.1187905380185525</v>
+        <v>-0.1339163398320844</v>
       </c>
       <c r="G5">
-        <v>0.09649686185027473</v>
+        <v>0.09984907932076113</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1257,10 +1248,10 @@
         <v>36</v>
       </c>
       <c r="F6">
-        <v>-0.3247096560964261</v>
+        <v>-0.308903728992286</v>
       </c>
       <c r="G6">
-        <v>0.1637317619592983</v>
+        <v>0.156812380506261</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1280,10 +1271,10 @@
         <v>36</v>
       </c>
       <c r="F7">
-        <v>-0.07100197455937352</v>
+        <v>-0.04309346119854718</v>
       </c>
       <c r="G7">
-        <v>0.1024578590512851</v>
+        <v>0.1071612407083845</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1349,10 +1340,10 @@
         <v>35</v>
       </c>
       <c r="F10">
-        <v>0.5943992644720945</v>
+        <v>0.5914574564271268</v>
       </c>
       <c r="G10">
-        <v>0.1534526917112568</v>
+        <v>0.1502436108957711</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1372,10 +1363,10 @@
         <v>35</v>
       </c>
       <c r="F11">
-        <v>0.2027421288282985</v>
+        <v>0.2157931262551407</v>
       </c>
       <c r="G11">
-        <v>0.06758499496325032</v>
+        <v>0.07285464428551176</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1395,10 +1386,10 @@
         <v>36</v>
       </c>
       <c r="F12">
-        <v>0.248078001954644</v>
+        <v>0.2344401719402113</v>
       </c>
       <c r="G12">
-        <v>0.179804117535258</v>
+        <v>0.1746178132863153</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1418,10 +1409,10 @@
         <v>36</v>
       </c>
       <c r="F13">
-        <v>0.08690259212808948</v>
+        <v>0.06282228613509133</v>
       </c>
       <c r="G13">
-        <v>0.06998776994440384</v>
+        <v>0.07286247446826231</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1487,10 +1478,10 @@
         <v>35</v>
       </c>
       <c r="F16">
-        <v>0.1683053232908135</v>
+        <v>0.1717544751431135</v>
       </c>
       <c r="G16">
-        <v>0.104446261093156</v>
+        <v>0.1025277187267522</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1510,10 +1501,10 @@
         <v>35</v>
       </c>
       <c r="F17">
-        <v>0.560475464969814</v>
+        <v>0.5451736943372381</v>
       </c>
       <c r="G17">
-        <v>0.06352499991810269</v>
+        <v>0.06111912442720431</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1533,10 +1524,10 @@
         <v>36</v>
       </c>
       <c r="F18">
-        <v>0.08801959422839248</v>
+        <v>0.1040094025152077</v>
       </c>
       <c r="G18">
-        <v>0.09525158442858499</v>
+        <v>0.1030461001161888</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1556,10 +1547,10 @@
         <v>36</v>
       </c>
       <c r="F19">
-        <v>0.1833047072749787</v>
+        <v>0.2115378994989614</v>
       </c>
       <c r="G19">
-        <v>0.06576551478397641</v>
+        <v>0.06608832474861839</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1625,10 +1616,10 @@
         <v>35</v>
       </c>
       <c r="F22">
-        <v>-0.2236039651502194</v>
+        <v>-0.2256576078705302</v>
       </c>
       <c r="G22">
-        <v>0.0786276478733048</v>
+        <v>0.07846120306783878</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1648,10 +1639,10 @@
         <v>35</v>
       </c>
       <c r="F23">
-        <v>-0.5645590708659549</v>
+        <v>-0.5554483180742076</v>
       </c>
       <c r="G23">
-        <v>0.08162601188147785</v>
+        <v>0.07922470000041328</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1671,10 +1662,10 @@
         <v>36</v>
       </c>
       <c r="F24">
-        <v>-0.1648244727684431</v>
+        <v>-0.17434488671181</v>
       </c>
       <c r="G24">
-        <v>0.09718144973020801</v>
+        <v>0.1024356384974356</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1694,10 +1685,10 @@
         <v>36</v>
       </c>
       <c r="F25">
-        <v>-0.2548314466946531</v>
+        <v>-0.2716416342900096</v>
       </c>
       <c r="G25">
-        <v>0.06304318391376751</v>
+        <v>0.06483607472105589</v>
       </c>
     </row>
   </sheetData>
@@ -2059,7 +2050,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -2485,7 +2476,7 @@
         <v>126</v>
       </c>
       <c r="B39" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="C39" t="s">
         <v>56</v>
@@ -2493,10 +2484,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B40" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C40" t="s">
         <v>56</v>
@@ -2504,10 +2495,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B41" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C41" t="s">
         <v>56</v>
@@ -2515,10 +2506,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B42" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C42" t="s">
         <v>56</v>
@@ -2526,54 +2517,54 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B43" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C43" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B44" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C44" t="s">
-        <v>137</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B45" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C45" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B46" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C46" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B47" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C47" t="s">
         <v>56</v>
@@ -2581,10 +2572,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C48" t="s">
         <v>56</v>
@@ -2592,10 +2583,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B49" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C49" t="s">
         <v>56</v>
@@ -2603,10 +2594,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B50" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C50" t="s">
         <v>56</v>
@@ -2614,10 +2605,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B51" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C51" t="s">
         <v>56</v>
@@ -2625,7 +2616,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B52" t="s">
         <v>115</v>
@@ -2636,10 +2627,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B53" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="C53" t="s">
         <v>56</v>
@@ -2647,10 +2638,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B54" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C54" t="s">
         <v>56</v>
@@ -2658,45 +2649,12 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B55" t="s">
-        <v>115</v>
+        <v>158</v>
       </c>
       <c r="C55" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" t="s">
-        <v>157</v>
-      </c>
-      <c r="B56" t="s">
-        <v>80</v>
-      </c>
-      <c r="C56" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" t="s">
-        <v>158</v>
-      </c>
-      <c r="B57" t="s">
-        <v>159</v>
-      </c>
-      <c r="C57" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" t="s">
-        <v>160</v>
-      </c>
-      <c r="B58" t="s">
-        <v>161</v>
-      </c>
-      <c r="C58" t="s">
         <v>56</v>
       </c>
     </row>

--- a/02_HRvLR_groups/Figures/S03_Signatures/c_data/s03_signatures.xlsx
+++ b/02_HRvLR_groups/Figures/S03_Signatures/c_data/s03_signatures.xlsx
@@ -8,18 +8,19 @@
   </bookViews>
   <sheets>
     <sheet name="read_me" sheetId="1" r:id="rId1"/>
-    <sheet name="pi_barcode" sheetId="2" r:id="rId2"/>
-    <sheet name="trajectory" sheetId="3" r:id="rId3"/>
-    <sheet name="window_stats" sheetId="4" r:id="rId4"/>
-    <sheet name="input_manifest" sheetId="5" r:id="rId5"/>
-    <sheet name="package_versions" sheetId="6" r:id="rId6"/>
+    <sheet name="columns" sheetId="2" r:id="rId2"/>
+    <sheet name="pi_barcode" sheetId="3" r:id="rId3"/>
+    <sheet name="trajectory" sheetId="4" r:id="rId4"/>
+    <sheet name="window_stats" sheetId="5" r:id="rId5"/>
+    <sheet name="input_manifest" sheetId="6" r:id="rId6"/>
+    <sheet name="package_versions" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="195">
   <si>
     <t>sheet</t>
   </si>
@@ -27,6 +28,12 @@
     <t>holds</t>
   </si>
   <si>
+    <t>columns</t>
+  </si>
+  <si>
+    <t>Every column of every sheet below, with what it holds.</t>
+  </si>
+  <si>
     <t>pi_barcode</t>
   </si>
   <si>
@@ -57,27 +64,132 @@
     <t>Packages loaded at run time.</t>
   </si>
   <si>
+    <t>column</t>
+  </si>
+  <si>
+    <t>meaning</t>
+  </si>
+  <si>
     <t>window</t>
   </si>
   <si>
+    <t>Time window or pairing: training (T2 - T1), acute (T3 - T2), baseline (T1 level against later change), baseline_level, post_level, post_bout_level (a level against trait levels); all or a time point in PERMANOVA.</t>
+  </si>
+  <si>
     <t>chosen</t>
   </si>
   <si>
+    <t>TRUE for the power used.</t>
+  </si>
+  <si>
     <t>ranked_in</t>
   </si>
   <si>
+    <t>Group whose ranking the set is placed in.</t>
+  </si>
+  <si>
     <t>direction</t>
   </si>
   <si>
+    <t>Direction of the change: Up or Down (Mixed when fry finds members moving both ways).</t>
+  </si>
+  <si>
     <t>n</t>
   </si>
   <si>
+    <t>Count for the row (proteins in the set, or sets called), as the sheet's read_me says.</t>
+  </si>
+  <si>
     <t>same_sign_share</t>
   </si>
   <si>
+    <t>Share of members moving the same way in both contrasts.</t>
+  </si>
+  <si>
     <t>fdr</t>
   </si>
   <si>
+    <t>Benjamini-Hochberg adjusted p-value, within the screen the read_me names.</t>
+  </si>
+  <si>
+    <t>set_from</t>
+  </si>
+  <si>
+    <t>Contrast whose p &lt; 0.05 proteins form the set.</t>
+  </si>
+  <si>
+    <t>set</t>
+  </si>
+  <si>
+    <t>Gene set name.</t>
+  </si>
+  <si>
+    <t>n_proteins</t>
+  </si>
+  <si>
+    <t>Proteins in the module or set.</t>
+  </si>
+  <si>
+    <t>arm</t>
+  </si>
+  <si>
+    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster arc.</t>
+  </si>
+  <si>
+    <t>timepoint</t>
+  </si>
+  <si>
+    <t>T1 baseline, T2 after training, T3 after the acute bout at the end of training.</t>
+  </si>
+  <si>
+    <t>mean_change</t>
+  </si>
+  <si>
+    <t>Mean change from each person's T1.</t>
+  </si>
+  <si>
+    <t>se</t>
+  </si>
+  <si>
+    <t>Standard error of the mean change.</t>
+  </si>
+  <si>
+    <t>input</t>
+  </si>
+  <si>
+    <t>Name the script gives the file it read.</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>Path of the file read.</t>
+  </si>
+  <si>
+    <t>md5</t>
+  </si>
+  <si>
+    <t>MD5 checksum of the file read.</t>
+  </si>
+  <si>
+    <t>package</t>
+  </si>
+  <si>
+    <t>R package.</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Package version.</t>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>Where the package came from.</t>
+  </si>
+  <si>
     <t>Training</t>
   </si>
   <si>
@@ -96,27 +208,6 @@
     <t>Acute</t>
   </si>
   <si>
-    <t>set_from</t>
-  </si>
-  <si>
-    <t>set</t>
-  </si>
-  <si>
-    <t>n_proteins</t>
-  </si>
-  <si>
-    <t>arm</t>
-  </si>
-  <si>
-    <t>timepoint</t>
-  </si>
-  <si>
-    <t>mean_change</t>
-  </si>
-  <si>
-    <t>se</t>
-  </si>
-  <si>
     <t>Training_HR</t>
   </si>
   <si>
@@ -138,42 +229,24 @@
     <t>Training_LR</t>
   </si>
   <si>
-    <t>input</t>
-  </si>
-  <si>
-    <t>path</t>
-  </si>
-  <si>
-    <t>md5</t>
-  </si>
-  <si>
     <t>contrasts</t>
   </si>
   <si>
-    <t>02_HRvLR_groups/02_DEP/c_data/02_contrasts.xlsx</t>
-  </si>
-  <si>
-    <t>4deff25d883e1dc54781cd410d78344b</t>
+    <t>02_HRvLR_groups/02_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
+  </si>
+  <si>
+    <t>a427c97768bcc7bf80a6526cbc8225f6</t>
   </si>
   <si>
     <t>set_tests</t>
   </si>
   <si>
-    <t>02_HRvLR_groups/03_Pathways/c_data/set_tests.rds</t>
+    <t>02_HRvLR_groups/03_Set_Contrasts/c_data/set_tests.rds</t>
   </si>
   <si>
     <t>068c220be1f09313a9955fa01f855602</t>
   </si>
   <si>
-    <t>package</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>source</t>
-  </si>
-  <si>
     <t>BiocGenerics</t>
   </si>
   <si>
@@ -192,6 +265,18 @@
     <t>CRAN (R 4.6.0)</t>
   </si>
   <si>
+    <t>bit</t>
+  </si>
+  <si>
+    <t>4.6.0</t>
+  </si>
+  <si>
+    <t>bit64</t>
+  </si>
+  <si>
+    <t>4.8.0</t>
+  </si>
+  <si>
     <t>cellranger</t>
   </si>
   <si>
@@ -321,6 +406,12 @@
     <t>1.0.2</t>
   </si>
   <si>
+    <t>hms</t>
+  </si>
+  <si>
+    <t>1.1.4</t>
+  </si>
+  <si>
     <t>IRanges</t>
   </si>
   <si>
@@ -405,6 +496,12 @@
     <t>1.1-3</t>
   </si>
   <si>
+    <t>readr</t>
+  </si>
+  <si>
+    <t>2.2.0</t>
+  </si>
+  <si>
     <t>readxl</t>
   </si>
   <si>
@@ -486,10 +583,22 @@
     <t>tidyselect</t>
   </si>
   <si>
+    <t>tzdb</t>
+  </si>
+  <si>
+    <t>0.5.0</t>
+  </si>
+  <si>
     <t>vctrs</t>
   </si>
   <si>
     <t>0.7.3</t>
+  </si>
+  <si>
+    <t>vroom</t>
+  </si>
+  <si>
+    <t>1.7.1</t>
   </si>
   <si>
     <t>withr</t>
@@ -838,7 +947,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
@@ -887,6 +996,14 @@
       </c>
       <c r="B6" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -896,214 +1013,315 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1">
+    <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2">
-        <v>14</v>
-      </c>
-      <c r="F2">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="G2">
-        <v>0.2530625944616725</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3">
-        <v>11</v>
-      </c>
-      <c r="F3">
-        <v>0.8181818181818182</v>
-      </c>
-      <c r="G3">
-        <v>0.2530625944616725</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4">
-        <v>7</v>
-      </c>
-      <c r="F4">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="G4">
-        <v>0.09058795812413797</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5">
-        <v>13</v>
-      </c>
-      <c r="F5">
-        <v>0.6923076923076923</v>
-      </c>
-      <c r="G5">
-        <v>0.06889464714178199</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6">
-        <v>44</v>
-      </c>
-      <c r="F6">
-        <v>0.6590909090909091</v>
-      </c>
-      <c r="G6">
-        <v>0.4227693516752487</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7">
-        <v>18</v>
-      </c>
-      <c r="F7">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="G7">
-        <v>0.4227693516752487</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8">
-        <v>21</v>
-      </c>
-      <c r="F8">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="G8">
-        <v>0.007170683951010844</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9">
+      <c r="B26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
         <v>12</v>
       </c>
-      <c r="F9">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="G9">
-        <v>0.007170683951010844</v>
+      <c r="B27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1113,582 +1331,214 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2">
-        <v>46</v>
+        <v>57</v>
+      </c>
+      <c r="C2" t="s">
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>34</v>
+        <v>59</v>
+      </c>
+      <c r="E2">
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.2530625944616725</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3">
-        <v>46</v>
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>34</v>
+        <v>60</v>
+      </c>
+      <c r="E3">
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.2530625944616725</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4">
-        <v>46</v>
+        <v>58</v>
+      </c>
+      <c r="C4" t="s">
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>35</v>
+        <v>59</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>-0.6143758522343953</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G4">
-        <v>0.1780293523942687</v>
+        <v>0.09058795812413797</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5">
-        <v>46</v>
+        <v>58</v>
+      </c>
+      <c r="C5" t="s">
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>35</v>
+        <v>60</v>
+      </c>
+      <c r="E5">
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>-0.1339163398320844</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="G5">
-        <v>0.09984907932076113</v>
+        <v>0.06889464714178199</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6">
-        <v>46</v>
+        <v>57</v>
+      </c>
+      <c r="C6" t="s">
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>36</v>
+        <v>60</v>
+      </c>
+      <c r="E6">
+        <v>44</v>
       </c>
       <c r="F6">
-        <v>-0.308903728992286</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="G6">
-        <v>0.156812380506261</v>
+        <v>0.4227693516752487</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7">
-        <v>46</v>
+        <v>57</v>
+      </c>
+      <c r="C7" t="s">
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" t="s">
-        <v>36</v>
+        <v>59</v>
+      </c>
+      <c r="E7">
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>-0.04309346119854718</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G7">
-        <v>0.1071612407083845</v>
+        <v>0.4227693516752487</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8">
-        <v>59</v>
+        <v>58</v>
+      </c>
+      <c r="C8" t="s">
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" t="s">
-        <v>34</v>
+        <v>60</v>
+      </c>
+      <c r="E8">
+        <v>21</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>0.007170683951010844</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9">
+        <v>58</v>
+      </c>
+      <c r="C9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" t="s">
         <v>59</v>
       </c>
-      <c r="D9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" t="s">
-        <v>34</v>
+      <c r="E9">
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10">
-        <v>59</v>
-      </c>
-      <c r="D10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10">
-        <v>0.5914574564271268</v>
-      </c>
-      <c r="G10">
-        <v>0.1502436108957711</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11">
-        <v>59</v>
-      </c>
-      <c r="D11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11">
-        <v>0.2157931262551407</v>
-      </c>
-      <c r="G11">
-        <v>0.07285464428551176</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12">
-        <v>59</v>
-      </c>
-      <c r="D12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12">
-        <v>0.2344401719402113</v>
-      </c>
-      <c r="G12">
-        <v>0.1746178132863153</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13">
-        <v>59</v>
-      </c>
-      <c r="D13" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13">
-        <v>0.06282228613509133</v>
-      </c>
-      <c r="G13">
-        <v>0.07286247446826231</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14">
-        <v>73</v>
-      </c>
-      <c r="D14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15">
-        <v>73</v>
-      </c>
-      <c r="D15" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" t="s">
-        <v>34</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16">
-        <v>73</v>
-      </c>
-      <c r="D16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" t="s">
-        <v>35</v>
-      </c>
-      <c r="F16">
-        <v>0.1717544751431135</v>
-      </c>
-      <c r="G16">
-        <v>0.1025277187267522</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17">
-        <v>73</v>
-      </c>
-      <c r="D17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" t="s">
-        <v>35</v>
-      </c>
-      <c r="F17">
-        <v>0.5451736943372381</v>
-      </c>
-      <c r="G17">
-        <v>0.06111912442720431</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18">
-        <v>73</v>
-      </c>
-      <c r="D18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18">
-        <v>0.1040094025152077</v>
-      </c>
-      <c r="G18">
-        <v>0.1030461001161888</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19">
-        <v>73</v>
-      </c>
-      <c r="D19" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19">
-        <v>0.2115378994989614</v>
-      </c>
-      <c r="G19">
-        <v>0.06608832474861839</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20">
-        <v>29</v>
-      </c>
-      <c r="D20" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" t="s">
-        <v>34</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21">
-        <v>29</v>
-      </c>
-      <c r="D21" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22">
-        <v>29</v>
-      </c>
-      <c r="D22" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" t="s">
-        <v>35</v>
-      </c>
-      <c r="F22">
-        <v>-0.2256576078705302</v>
-      </c>
-      <c r="G22">
-        <v>0.07846120306783878</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23">
-        <v>29</v>
-      </c>
-      <c r="D23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" t="s">
-        <v>35</v>
-      </c>
-      <c r="F23">
-        <v>-0.5554483180742076</v>
-      </c>
-      <c r="G23">
-        <v>0.07922470000041328</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24">
-        <v>29</v>
-      </c>
-      <c r="D24" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" t="s">
-        <v>36</v>
-      </c>
-      <c r="F24">
-        <v>-0.17434488671181</v>
-      </c>
-      <c r="G24">
-        <v>0.1024356384974356</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25">
-        <v>29</v>
-      </c>
-      <c r="D25" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" t="s">
-        <v>36</v>
-      </c>
-      <c r="F25">
-        <v>-0.2716416342900096</v>
-      </c>
-      <c r="G25">
-        <v>0.06483607472105589</v>
+        <v>0.007170683951010844</v>
       </c>
     </row>
   </sheetData>
@@ -1698,306 +1548,582 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
+        <v>63</v>
+      </c>
+      <c r="C2">
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2">
-        <v>59</v>
+        <v>57</v>
+      </c>
+      <c r="E2" t="s">
+        <v>64</v>
       </c>
       <c r="F2">
-        <v>0.8983050847457628</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>0.136251863706479</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
+        <v>63</v>
+      </c>
+      <c r="C3">
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3">
-        <v>46</v>
+        <v>58</v>
+      </c>
+      <c r="E3" t="s">
+        <v>64</v>
       </c>
       <c r="F3">
-        <v>0.7391304347826086</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>0.2530625944616725</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
+        <v>63</v>
+      </c>
+      <c r="C4">
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4">
-        <v>73</v>
+        <v>57</v>
+      </c>
+      <c r="E4" t="s">
+        <v>65</v>
       </c>
       <c r="F4">
-        <v>0.821917808219178</v>
+        <v>-0.6143758522343953</v>
       </c>
       <c r="G4">
-        <v>0.01553912266263835</v>
+        <v>0.1780293523942687</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
+        <v>63</v>
+      </c>
+      <c r="C5">
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5">
-        <v>29</v>
+        <v>58</v>
+      </c>
+      <c r="E5" t="s">
+        <v>65</v>
       </c>
       <c r="F5">
-        <v>0.7586206896551724</v>
+        <v>-0.1339163398320844</v>
       </c>
       <c r="G5">
-        <v>0.02621198476206677</v>
+        <v>0.09984907932076113</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
+        <v>63</v>
+      </c>
+      <c r="C6">
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6">
-        <v>46</v>
+        <v>57</v>
+      </c>
+      <c r="E6" t="s">
+        <v>66</v>
       </c>
       <c r="F6">
-        <v>0.108695652173913</v>
+        <v>-0.308903728992286</v>
       </c>
       <c r="G6">
-        <v>0.00512622613304799</v>
+        <v>0.156812380506261</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
+        <v>63</v>
+      </c>
+      <c r="C7">
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7">
-        <v>59</v>
+        <v>58</v>
+      </c>
+      <c r="E7" t="s">
+        <v>66</v>
       </c>
       <c r="F7">
-        <v>0.0847457627118644</v>
+        <v>-0.04309346119854718</v>
       </c>
       <c r="G7">
-        <v>0.00512622613304799</v>
+        <v>0.1071612407083845</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>24</v>
+        <v>67</v>
+      </c>
+      <c r="C8">
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8">
-        <v>59</v>
+        <v>57</v>
+      </c>
+      <c r="E8" t="s">
+        <v>64</v>
       </c>
       <c r="F8">
-        <v>0.2711864406779661</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>0.6412446112952916</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>24</v>
+        <v>67</v>
+      </c>
+      <c r="C9">
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9">
-        <v>46</v>
+        <v>58</v>
+      </c>
+      <c r="E9" t="s">
+        <v>64</v>
       </c>
       <c r="F9">
-        <v>0.4565217391304348</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>0.9152485596162396</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
+        <v>67</v>
+      </c>
+      <c r="C10">
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10">
-        <v>73</v>
+        <v>57</v>
+      </c>
+      <c r="E10" t="s">
+        <v>65</v>
       </c>
       <c r="F10">
-        <v>0.0273972602739726</v>
+        <v>0.5914574564271268</v>
       </c>
       <c r="G10">
-        <v>1.060179368760575E-05</v>
+        <v>0.1502436108957711</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" t="s">
-        <v>24</v>
+        <v>67</v>
+      </c>
+      <c r="C11">
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11">
-        <v>29</v>
+        <v>58</v>
+      </c>
+      <c r="E11" t="s">
+        <v>65</v>
       </c>
       <c r="F11">
-        <v>0.103448275862069</v>
+        <v>0.2157931262551407</v>
       </c>
       <c r="G11">
-        <v>0.001081815375941551</v>
+        <v>0.07285464428551176</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" t="s">
-        <v>24</v>
+        <v>67</v>
+      </c>
+      <c r="C12">
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12">
-        <v>73</v>
+        <v>57</v>
+      </c>
+      <c r="E12" t="s">
+        <v>66</v>
       </c>
       <c r="F12">
-        <v>0.3013698630136986</v>
+        <v>0.2344401719402113</v>
       </c>
       <c r="G12">
-        <v>0.1266559257519356</v>
+        <v>0.1746178132863153</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
+        <v>67</v>
+      </c>
+      <c r="C13">
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13">
+        <v>58</v>
+      </c>
+      <c r="E13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13">
+        <v>0.06282228613509133</v>
+      </c>
+      <c r="G13">
+        <v>0.07286247446826231</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14">
+        <v>73</v>
+      </c>
+      <c r="D14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15">
+        <v>73</v>
+      </c>
+      <c r="D15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16">
+        <v>73</v>
+      </c>
+      <c r="D16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16">
+        <v>0.1717544751431135</v>
+      </c>
+      <c r="G16">
+        <v>0.1025277187267522</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17">
+        <v>73</v>
+      </c>
+      <c r="D17" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17">
+        <v>0.5451736943372381</v>
+      </c>
+      <c r="G17">
+        <v>0.06111912442720431</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18">
+        <v>73</v>
+      </c>
+      <c r="D18" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18">
+        <v>0.1040094025152077</v>
+      </c>
+      <c r="G18">
+        <v>0.1030461001161888</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19">
+        <v>73</v>
+      </c>
+      <c r="D19" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19">
+        <v>0.2115378994989614</v>
+      </c>
+      <c r="G19">
+        <v>0.06608832474861839</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20">
         <v>29</v>
       </c>
-      <c r="F13">
-        <v>0.4482758620689655</v>
-      </c>
-      <c r="G13">
-        <v>0.5682045687999953</v>
+      <c r="D20" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21">
+        <v>29</v>
+      </c>
+      <c r="D21" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22">
+        <v>29</v>
+      </c>
+      <c r="D22" t="s">
+        <v>57</v>
+      </c>
+      <c r="E22" t="s">
+        <v>65</v>
+      </c>
+      <c r="F22">
+        <v>-0.2256576078705302</v>
+      </c>
+      <c r="G22">
+        <v>0.07846120306783878</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23">
+        <v>29</v>
+      </c>
+      <c r="D23" t="s">
+        <v>58</v>
+      </c>
+      <c r="E23" t="s">
+        <v>65</v>
+      </c>
+      <c r="F23">
+        <v>-0.5554483180742076</v>
+      </c>
+      <c r="G23">
+        <v>0.07922470000041328</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24">
+        <v>29</v>
+      </c>
+      <c r="D24" t="s">
+        <v>57</v>
+      </c>
+      <c r="E24" t="s">
+        <v>66</v>
+      </c>
+      <c r="F24">
+        <v>-0.17434488671181</v>
+      </c>
+      <c r="G24">
+        <v>0.1024356384974356</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25">
+        <v>29</v>
+      </c>
+      <c r="D25" t="s">
+        <v>58</v>
+      </c>
+      <c r="E25" t="s">
+        <v>66</v>
+      </c>
+      <c r="F25">
+        <v>-0.2716416342900096</v>
+      </c>
+      <c r="G25">
+        <v>0.06483607472105589</v>
       </c>
     </row>
   </sheetData>
@@ -2007,40 +2133,306 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1">
+    <row r="1" spans="1:7" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2">
+        <v>59</v>
+      </c>
+      <c r="F2">
+        <v>0.8983050847457628</v>
+      </c>
+      <c r="G2">
+        <v>0.136251863706479</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3">
         <v>46</v>
       </c>
-      <c r="C3" t="s">
-        <v>47</v>
+      <c r="F3">
+        <v>0.7391304347826086</v>
+      </c>
+      <c r="G3">
+        <v>0.2530625944616725</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4">
+        <v>73</v>
+      </c>
+      <c r="F4">
+        <v>0.821917808219178</v>
+      </c>
+      <c r="G4">
+        <v>0.01553912266263835</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5">
+        <v>29</v>
+      </c>
+      <c r="F5">
+        <v>0.7586206896551724</v>
+      </c>
+      <c r="G5">
+        <v>0.02621198476206677</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6">
+        <v>46</v>
+      </c>
+      <c r="F6">
+        <v>0.108695652173913</v>
+      </c>
+      <c r="G6">
+        <v>0.00512622613304799</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7">
+        <v>59</v>
+      </c>
+      <c r="F7">
+        <v>0.0847457627118644</v>
+      </c>
+      <c r="G7">
+        <v>0.00512622613304799</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8">
+        <v>59</v>
+      </c>
+      <c r="F8">
+        <v>0.2711864406779661</v>
+      </c>
+      <c r="G8">
+        <v>0.6412446112952916</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9">
+        <v>46</v>
+      </c>
+      <c r="F9">
+        <v>0.4565217391304348</v>
+      </c>
+      <c r="G9">
+        <v>0.9152485596162396</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10">
+        <v>73</v>
+      </c>
+      <c r="F10">
+        <v>0.0273972602739726</v>
+      </c>
+      <c r="G10">
+        <v>1.060179368760575E-05</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11">
+        <v>29</v>
+      </c>
+      <c r="F11">
+        <v>0.103448275862069</v>
+      </c>
+      <c r="G11">
+        <v>0.001081815375941551</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12">
+        <v>73</v>
+      </c>
+      <c r="F12">
+        <v>0.3013698630136986</v>
+      </c>
+      <c r="G12">
+        <v>0.1266559257519356</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13">
+        <v>29</v>
+      </c>
+      <c r="F13">
+        <v>0.4482758620689655</v>
+      </c>
+      <c r="G13">
+        <v>0.5682045687999953</v>
       </c>
     </row>
   </sheetData>
@@ -2050,612 +2442,721 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C61"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>54</v>
       </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>78</v>
+      </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="C22" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="C23" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="C24" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="C25" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="C26" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="B28" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="C28" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="B30" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="C30" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="B31" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="C31" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="C32" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="B33" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="C33" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="B34" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="C34" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="B35" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="C35" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="B36" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="C36" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="C37" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="B38" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="C38" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="B39" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="C39" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="B40" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="C40" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="B41" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="C41" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="B42" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="C42" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="B43" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="C43" t="s">
-        <v>136</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="B44" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="C44" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="B45" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="C45" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="B46" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C46" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="B47" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="C47" t="s">
-        <v>56</v>
+        <v>168</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="B48" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C48" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="B49" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="C49" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="B50" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="C50" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="B51" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="C51" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="B52" t="s">
-        <v>115</v>
+        <v>178</v>
       </c>
       <c r="C52" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="B53" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="C53" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="B54" t="s">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="C54" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="B55" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="C55" t="s">
-        <v>56</v>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>185</v>
+      </c>
+      <c r="B56" t="s">
+        <v>145</v>
+      </c>
+      <c r="C56" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>186</v>
+      </c>
+      <c r="B57" t="s">
+        <v>108</v>
+      </c>
+      <c r="C57" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>187</v>
+      </c>
+      <c r="B58" t="s">
+        <v>188</v>
+      </c>
+      <c r="C58" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>189</v>
+      </c>
+      <c r="B59" t="s">
+        <v>190</v>
+      </c>
+      <c r="C59" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>191</v>
+      </c>
+      <c r="B60" t="s">
+        <v>192</v>
+      </c>
+      <c r="C60" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>193</v>
+      </c>
+      <c r="B61" t="s">
+        <v>194</v>
+      </c>
+      <c r="C61" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/02_HRvLR_groups/Figures/S03_Signatures/c_data/s03_signatures.xlsx
+++ b/02_HRvLR_groups/Figures/S03_Signatures/c_data/s03_signatures.xlsx
@@ -235,7 +235,7 @@
     <t>02_HRvLR_groups/02_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>a427c97768bcc7bf80a6526cbc8225f6</t>
+    <t>f3294b7f02df2c8ee462be5604fcd0a5</t>
   </si>
   <si>
     <t>set_tests</t>
@@ -244,7 +244,7 @@
     <t>02_HRvLR_groups/03_Set_Contrasts/c_data/set_tests.rds</t>
   </si>
   <si>
-    <t>068c220be1f09313a9955fa01f855602</t>
+    <t>b928dfb75f0631b92e8ffaf819778f86</t>
   </si>
   <si>
     <t>BiocGenerics</t>

--- a/02_HRvLR_groups/Figures/S03_Signatures/c_data/s03_signatures.xlsx
+++ b/02_HRvLR_groups/Figures/S03_Signatures/c_data/s03_signatures.xlsx
@@ -133,7 +133,7 @@
     <t>arm</t>
   </si>
   <si>
-    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster arc.</t>
+    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster grouping.</t>
   </si>
   <si>
     <t>timepoint</t>
@@ -235,7 +235,7 @@
     <t>02_HRvLR_groups/02_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>f3294b7f02df2c8ee462be5604fcd0a5</t>
+    <t>e02599bb8f2c5a55f975346edd987fb0</t>
   </si>
   <si>
     <t>set_tests</t>

--- a/02_HRvLR_groups/Figures/S03_Signatures/c_data/s03_signatures.xlsx
+++ b/02_HRvLR_groups/Figures/S03_Signatures/c_data/s03_signatures.xlsx
@@ -235,7 +235,7 @@
     <t>02_HRvLR_groups/02_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>e02599bb8f2c5a55f975346edd987fb0</t>
+    <t>0d6cf853ff8d0d35c8767a6734aeecb9</t>
   </si>
   <si>
     <t>set_tests</t>
